--- a/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
+++ b/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Архитектура аппаратных средств: состав и уровни»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, из каких уровней собрана вычислительная система: от прикладной программы через драйвер и шину до конкретного устройства.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура аппаратных средств: состав и уровни</t>
+          <t xml:space="preserve">уровень абстракции, драйвер, шина, периферия, платформа</t>
         </is>
       </c>
     </row>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Представление данных в компьютере»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, как число, символ и адрес превращаются в двоичный код, и почему разрядность задаёт предел представимых значений.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Представление данных в компьютере</t>
+          <t xml:space="preserve">разрядность, дополнительный код, шестнадцатеричная запись, кодировка, переполнение</t>
         </is>
       </c>
     </row>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Разбор конфигурации ПК; Расчёт объёма памяти и накопителя.</t>
+          <t xml:space="preserve">Собираете паспорт учебного ПК по данным системы и считаете, сколько памяти нужно под набор программ, сдавая таблицу расчёта.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор конфигурации ПК, Расчёт объёма памяти и накопителя</t>
+          <t xml:space="preserve">паспорт ПК, гибибайт, запас ёмкости, системный отчёт, объём данных</t>
         </is>
       </c>
     </row>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Логические элементы и схемы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь собирать сумму и сравнение из базовых логических элементов и читать таблицу истинности как описание схемы.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Логические элементы и схемы</t>
+          <t xml:space="preserve">AND, OR, NOT, таблица истинности, полусумматор, вентиль</t>
         </is>
       </c>
     </row>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Анализ процессора и кэша»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Определяете модель процессора, число ядер и объём кэша по системным данным и сравниваете два учебных ПК, сдавая таблицу сравнения.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ процессора и кэша</t>
+          <t xml:space="preserve">ядро, тактовая частота, кэш L2, системный отчёт, сравнение</t>
         </is>
       </c>
     </row>
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Процессор: состав и принцип работы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте цикл выборки и исполнения команды и увидите, какие блоки процессора участвуют на каждом шаге.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Процессор: состав и принцип работы</t>
+          <t xml:space="preserve">АЛУ, устройство управления, регистр, счётчик команд, дешифратор</t>
         </is>
       </c>
     </row>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Система команд и регистры»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, из чего состоит команда, зачем нужны регистры общего назначения и как адресация задаёт место операнда.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Система команд и регистры</t>
+          <t xml:space="preserve">код операции, операнд, аккумулятор, адресация, флаги</t>
         </is>
       </c>
     </row>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сравнение HDD и SSD; RAID: расчёт и отказоустойчивость.</t>
+          <t xml:space="preserve">Сравниваете накопители по скорости и цене гигабайта и считаете полезный объём массивов RAID, сдавая таблицу с выводами.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравнение HDD и SSD, RAID: расчёт и отказоустойчивость</t>
+          <t xml:space="preserve">время доступа, цена гигабайта, чётность, полезная ёмкость, отказ диска</t>
         </is>
       </c>
     </row>
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Конвейер и производительность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Поймёте, как конвейер ускоряет поток команд, откуда берутся простои и почему тактовая частота не единственный показатель.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Конвейер и производительность</t>
+          <t xml:space="preserve">стадия конвейера, такт, простой, конфликт данных, предсказание перехода</t>
         </is>
       </c>
     </row>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Выбор серверной платформы»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Подбираете сервер под учебную нагрузку: считаете ядра, память и диски и обосновываете выбор в таблице сравнения трёх вариантов.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выбор серверной платформы</t>
+          <t xml:space="preserve">нагрузка, ядро, стоимость владения, масштабирование, обоснование</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Память: иерархия и кэш»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте пирамиду памяти и то, как кэш сокращает обращения к оперативной памяти за счёт локальности данных.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Память: иерархия и кэш</t>
+          <t xml:space="preserve">регистр, кэш L1, оперативная память, локальность, промах кэша</t>
         </is>
       </c>
     </row>
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оперативная память»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, чем DDR отличается от DDR4 и DDR5, что даёт двухканальный режим и почему планки разной частоты работают на меньшей.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оперативная память</t>
+          <t xml:space="preserve">DDR4, DDR5, двухканальный режим, тайминг, форм-фактор DIMM</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Виртуализация в VirtualBox; Диагностика аппаратных проблем.</t>
+          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox и разбираете учебный сбой по признакам, сдавая настройки ВМ и таблицу диагностики.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуализация в VirtualBox, Диагностика аппаратных проблем</t>
+          <t xml:space="preserve">виртуальная машина, выделение памяти, признак сбоя, порядок проверки, журнал</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Постоянная память и BIOS/UEFI»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проследите путь включения компьютера от прошивки до загрузки системы и увидите, какие настройки UEFI влияют на старт.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Постоянная память и BIOS/UEFI</t>
+          <t xml:space="preserve">POST, CMOS, Legacy, загрузочная запись, Secure Boot</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Модернизация учебного ПК»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Составляете план модернизации учебного ПК под задачу и бюджет и обосновываете замену деталей, сдавая смету и порядок работ.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Модернизация учебного ПК</t>
+          <t xml:space="preserve">узкое место, совместимость, смета, блок питания, порядок работ</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Системная шина и интерфейсы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните шины и интерфейсы по пропускной способности и поймёте, какое устройство куда подключать и почему скорость падает.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Системная шина и интерфейсы</t>
+          <t xml:space="preserve">PCIe, SATA, USB, пропускная способность, линия связи, контроллер</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Энергопотребление и охлаждение»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Считаете мощность сборки и подбираете охлаждение под тепловыделение, сдавая расчёт с запасом по блоку питания.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энергопотребление и охлаждение</t>
+          <t xml:space="preserve">тепловыделение, TDP, запас мощности, теплотрубка, воздушный поток</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Чипсет и материнская плата»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, какие линии процессора идут напрямую, что берёт на себя чипсет и как форм-фактор ограничивает сборку.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чипсет и материнская плата</t>
+          <t xml:space="preserve">PCH, сокет, форм-фактор, линия PCIe, разъём M.2</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая работа: конфигурация под ИС»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете конфигурацию под учебную информационную систему и защищаете её: требования, смета, обоснование каждого узла.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая работа: конфигурация под ИС</t>
+          <t xml:space="preserve">требования, смета, профиль нагрузки, резерв, защита конфигурации</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Накопители HDD и SSD»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте устройство жёсткого диска и твердотельного накопителя и поймёте, почему SSD быстрее на случайном чтении.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Накопители HDD и SSD</t>
+          <t xml:space="preserve">пластина, головка, NAND, контроллер, TBW, фрагментация</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «RAID и хранение данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните уровни RAID по отказоустойчивости и полезной ёмкости и научитесь выбирать массив под задачу хранения.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAID и хранение данных</t>
+          <t xml:space="preserve">зеркало, чётность, страйп, горячая замена, полезная ёмкость</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Видеоподсистема»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, из чего состоит видеокарта, зачем нужна видеопамять и как разрешение и частота кадров нагружают графический процессор.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Видеоподсистема</t>
+          <t xml:space="preserve">графический процессор, видеопамять, GDDR, разрешение, частота кадров, интерфейс вывода</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Устройства ввода и вывода»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните устройства ввода и вывода по принципу действия и разберётесь, какой интерфейс и драйвер нужен каждому.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Устройства ввода и вывода</t>
+          <t xml:space="preserve">сканер, принтер, матрица, HID, драйвер, разрешение печати</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Питание и охлаждение»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, как блок питания распределяет мощность по линиям и почему перегрев снижает частоту процессора.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Питание и охлаждение</t>
+          <t xml:space="preserve">линия 12 В, КПД, троттлинг, радиатор, термопаста, тепловой пакет</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Мобильные и встраиваемые платформы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните ноутбук, планшет и встраиваемую плату по энергопотреблению, компоновке и возможностям модернизации.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильные и встраиваемые платформы</t>
+          <t xml:space="preserve">SoC, энергоэффективность, пассивное охлаждение, распаянная память, микроконтроллер</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Серверные платформы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, чем сервер отличается от настольного ПК: резервирование питания, память с коррекцией и горячая замена дисков.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серверные платформы</t>
+          <t xml:space="preserve">ECC, резервирование, стойка, горячая замена, IPMI</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виртуализация аппаратных ресурсов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проследите, как гипервизор делит процессор, память и диски между виртуальными машинами и где теряется производительность.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуализация аппаратных ресурсов</t>
+          <t xml:space="preserve">гипервизор, виртуальный диск, оверкоммит, снапшот, аппаратное ускорение</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Выбор конфигурации под задачу»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь переводить требования задачи в характеристики узлов и находить узкое место до покупки, а не после.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выбор конфигурации под задачу</t>
+          <t xml:space="preserve">профиль нагрузки, узкое место, бюджет, запас роста, требования</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диагностика и модернизация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте порядок поиска неисправности от простых причин к сложным и научитесь отличать сбой железа от сбоя системы.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика и модернизация</t>
+          <t xml:space="preserve">признак неисправности, метод замены, журнал событий, тест памяти, замена детали</t>
         </is>
       </c>
     </row>

--- a/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
+++ b/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>2880</v>
+        <v>64</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>

--- a/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
+++ b/courses/2/architecture/dist/Учебный_план_Архитектура_аппаратных_средств.xlsx
@@ -302,12 +302,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Анализ процессора и кэша</t>
+          <t xml:space="preserve">Лекция 4. Процессор: состав и принцип работы</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Определяете модель процессора, число ядер и объём кэша по системным данным и сравниваете два учебных ПК, сдавая таблицу сравнения.</t>
+          <t xml:space="preserve">Разберёте цикл выборки и исполнения команды и увидите, какие блоки процессора участвуют на каждом шаге.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ядро, тактовая частота, кэш L2, системный отчёт, сравнение</t>
+          <t xml:space="preserve">АЛУ, устройство управления, регистр, счётчик команд, дешифратор</t>
         </is>
       </c>
     </row>
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Процессор: состав и принцип работы</t>
+          <t xml:space="preserve">Лекция 5. Система команд и регистры</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте цикл выборки и исполнения команды и увидите, какие блоки процессора участвуют на каждом шаге.</t>
+          <t xml:space="preserve">Разберёте, из чего состоит команда, зачем нужны регистры общего назначения и как адресация задаёт место операнда.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">АЛУ, устройство управления, регистр, счётчик команд, дешифратор</t>
+          <t xml:space="preserve">код операции, операнд, аккумулятор, адресация, флаги</t>
         </is>
       </c>
     </row>
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Система команд и регистры</t>
+          <t xml:space="preserve">Лекция 6. Конвейер и производительность</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,59 +375,59 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, из чего состоит команда, зачем нужны регистры общего назначения и как адресация задаёт место операнда.</t>
+          <t xml:space="preserve">Поймёте, как конвейер ускоряет поток команд, откуда берутся простои и почему тактовая частота не единственный показатель.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">код операции, операнд, аккумулятор, адресация, флаги</t>
+          <t xml:space="preserve">стадия конвейера, такт, простой, конфликт данных, предсказание перехода</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Сравнение HDD и SSD; RAID: расчёт и отказоустойчивость</t>
+          <t xml:space="preserve">Лекция 7. Память: иерархия и кэш</t>
         </is>
       </c>
       <c r="D13" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравниваете накопители по скорости и цене гигабайта и считаете полезный объём массивов RAID, сдавая таблицу с выводами.</t>
+          <t xml:space="preserve">Разберёте пирамиду памяти и то, как кэш сокращает обращения к оперативной памяти за счёт локальности данных.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">время доступа, цена гигабайта, чётность, полезная ёмкость, отказ диска</t>
+          <t xml:space="preserve">регистр, кэш L1, оперативная память, локальность, промах кэша</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Конвейер и производительность</t>
+          <t xml:space="preserve">Практика 2. Анализ процессора и кэша</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -435,29 +435,29 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поймёте, как конвейер ускоряет поток команд, откуда берутся простои и почему тактовая частота не единственный показатель.</t>
+          <t xml:space="preserve">Определяете модель процессора, число ядер и объём кэша по системным данным и сравниваете два учебных ПК, сдавая таблицу сравнения.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">стадия конвейера, такт, простой, конфликт данных, предсказание перехода</t>
+          <t xml:space="preserve">ядро, тактовая частота, кэш L2, системный отчёт, сравнение</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Выбор серверной платформы</t>
+          <t xml:space="preserve">Лекция 8. Оперативная память</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,19 +465,19 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подбираете сервер под учебную нагрузку: считаете ядра, память и диски и обосновываете выбор в таблице сравнения трёх вариантов.</t>
+          <t xml:space="preserve">Разберёте, чем DDR отличается от DDR4 и DDR5, что даёт двухканальный режим и почему планки разной частоты работают на меньшей.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">нагрузка, ядро, стоимость владения, масштабирование, обоснование</t>
+          <t xml:space="preserve">DDR4, DDR5, двухканальный режим, тайминг, форм-фактор DIMM</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Память: иерархия и кэш</t>
+          <t xml:space="preserve">Лекция 9. Постоянная память и BIOS/UEFI</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,19 +495,19 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте пирамиду памяти и то, как кэш сокращает обращения к оперативной памяти за счёт локальности данных.</t>
+          <t xml:space="preserve">Проследите путь включения компьютера от прошивки до загрузки системы и увидите, какие настройки UEFI влияют на старт.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">регистр, кэш L1, оперативная память, локальность, промах кэша</t>
+          <t xml:space="preserve">POST, CMOS, Legacy, загрузочная запись, Secure Boot</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Оперативная память</t>
+          <t xml:space="preserve">Лекция 10. Системная шина и интерфейсы</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,49 +525,49 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, чем DDR отличается от DDR4 и DDR5, что даёт двухканальный режим и почему планки разной частоты работают на меньшей.</t>
+          <t xml:space="preserve">Сравните шины и интерфейсы по пропускной способности и поймёте, какое устройство куда подключать и почему скорость падает.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDR4, DDR5, двухканальный режим, тайминг, форм-фактор DIMM</t>
+          <t xml:space="preserve">PCIe, SATA, USB, пропускная способность, линия связи, контроллер</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Виртуализация в VirtualBox; Диагностика аппаратных проблем</t>
+          <t xml:space="preserve">Лекция 11. Чипсет и материнская плата</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox и разбираете учебный сбой по признакам, сдавая настройки ВМ и таблицу диагностики.</t>
+          <t xml:space="preserve">Разберёте, какие линии процессора идут напрямую, что берёт на себя чипсет и как форм-фактор ограничивает сборку.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">виртуальная машина, выделение памяти, признак сбоя, порядок проверки, журнал</t>
+          <t xml:space="preserve">PCH, сокет, форм-фактор, линия PCIe, разъём M.2</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Постоянная память и BIOS/UEFI</t>
+          <t xml:space="preserve">Лекция 12. Накопители HDD и SSD</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,29 +585,29 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проследите путь включения компьютера от прошивки до загрузки системы и увидите, какие настройки UEFI влияют на старт.</t>
+          <t xml:space="preserve">Разберёте устройство жёсткого диска и твердотельного накопителя и поймёте, почему SSD быстрее на случайном чтении.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">POST, CMOS, Legacy, загрузочная запись, Secure Boot</t>
+          <t xml:space="preserve">пластина, головка, NAND, контроллер, TBW, фрагментация</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Модернизация учебного ПК</t>
+          <t xml:space="preserve">Лекция 13. RAID и хранение данных</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,59 +615,59 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Составляете план модернизации учебного ПК под задачу и бюджет и обосновываете замену деталей, сдавая смету и порядок работ.</t>
+          <t xml:space="preserve">Сравните уровни RAID по отказоустойчивости и полезной ёмкости и научитесь выбирать массив под задачу хранения.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">узкое место, совместимость, смета, блок питания, порядок работ</t>
+          <t xml:space="preserve">зеркало, чётность, страйп, горячая замена, полезная ёмкость</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">17-18</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Системная шина и интерфейсы</t>
+          <t xml:space="preserve">Практика 3. Сравнение HDD и SSD; RAID: расчёт и отказоустойчивость</t>
         </is>
       </c>
       <c r="D21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните шины и интерфейсы по пропускной способности и поймёте, какое устройство куда подключать и почему скорость падает.</t>
+          <t xml:space="preserve">Сравниваете накопители по скорости и цене гигабайта и считаете полезный объём массивов RAID, сдавая таблицу с выводами.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIe, SATA, USB, пропускная способность, линия связи, контроллер</t>
+          <t xml:space="preserve">время доступа, цена гигабайта, чётность, полезная ёмкость, отказ диска</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Энергопотребление и охлаждение</t>
+          <t xml:space="preserve">Лекция 14. Видеоподсистема</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,19 +675,19 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Считаете мощность сборки и подбираете охлаждение под тепловыделение, сдавая расчёт с запасом по блоку питания.</t>
+          <t xml:space="preserve">Разберёте, из чего состоит видеокарта, зачем нужна видеопамять и как разрешение и частота кадров нагружают графический процессор.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">тепловыделение, TDP, запас мощности, теплотрубка, воздушный поток</t>
+          <t xml:space="preserve">графический процессор, видеопамять, GDDR, разрешение, частота кадров, интерфейс вывода</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Чипсет и материнская плата</t>
+          <t xml:space="preserve">Лекция 15. Устройства ввода и вывода</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,29 +705,29 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, какие линии процессора идут напрямую, что берёт на себя чипсет и как форм-фактор ограничивает сборку.</t>
+          <t xml:space="preserve">Сравните устройства ввода и вывода по принципу действия и разберётесь, какой интерфейс и драйвер нужен каждому.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCH, сокет, форм-фактор, линия PCIe, разъём M.2</t>
+          <t xml:space="preserve">сканер, принтер, матрица, HID, драйвер, разрешение печати</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Итоговая работа: конфигурация под ИС</t>
+          <t xml:space="preserve">Лекция 16. Питание и охлаждение</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,29 +735,29 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете конфигурацию под учебную информационную систему и защищаете её: требования, смета, обоснование каждого узла.</t>
+          <t xml:space="preserve">Разберёте, как блок питания распределяет мощность по линиям и почему перегрев снижает частоту процессора.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">требования, смета, профиль нагрузки, резерв, защита конфигурации</t>
+          <t xml:space="preserve">линия 12 В, КПД, троттлинг, радиатор, термопаста, тепловой пакет</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Накопители HDD и SSD</t>
+          <t xml:space="preserve">Практика 4. Энергопотребление и охлаждение</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,19 +765,19 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте устройство жёсткого диска и твердотельного накопителя и поймёте, почему SSD быстрее на случайном чтении.</t>
+          <t xml:space="preserve">Считаете мощность сборки и подбираете охлаждение под тепловыделение, сдавая расчёт с запасом по блоку питания.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">пластина, головка, NAND, контроллер, TBW, фрагментация</t>
+          <t xml:space="preserve">тепловыделение, TDP, запас мощности, теплотрубка, воздушный поток</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. RAID и хранение данных</t>
+          <t xml:space="preserve">Лекция 17. Мобильные и встраиваемые платформы</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,19 +795,19 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните уровни RAID по отказоустойчивости и полезной ёмкости и научитесь выбирать массив под задачу хранения.</t>
+          <t xml:space="preserve">Сравните ноутбук, планшет и встраиваемую плату по энергопотреблению, компоновке и возможностям модернизации.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">зеркало, чётность, страйп, горячая замена, полезная ёмкость</t>
+          <t xml:space="preserve">SoC, энергоэффективность, пассивное охлаждение, распаянная память, микроконтроллер</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Видеоподсистема</t>
+          <t xml:space="preserve">Лекция 18. Серверные платформы</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,29 +825,29 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, из чего состоит видеокарта, зачем нужна видеопамять и как разрешение и частота кадров нагружают графический процессор.</t>
+          <t xml:space="preserve">Разберёте, чем сервер отличается от настольного ПК: резервирование питания, память с коррекцией и горячая замена дисков.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">графический процессор, видеопамять, GDDR, разрешение, частота кадров, интерфейс вывода</t>
+          <t xml:space="preserve">ECC, резервирование, стойка, горячая замена, IPMI</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Устройства ввода и вывода</t>
+          <t xml:space="preserve">Практика 5. Выбор серверной платформы</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,19 +855,19 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните устройства ввода и вывода по принципу действия и разберётесь, какой интерфейс и драйвер нужен каждому.</t>
+          <t xml:space="preserve">Подбираете сервер под учебную нагрузку: считаете ядра, память и диски и обосновываете выбор в таблице сравнения трёх вариантов.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сканер, принтер, матрица, HID, драйвер, разрешение печати</t>
+          <t xml:space="preserve">нагрузка, ядро, стоимость владения, масштабирование, обоснование</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Питание и охлаждение</t>
+          <t xml:space="preserve">Лекция 19. Виртуализация аппаратных ресурсов</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,19 +885,19 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, как блок питания распределяет мощность по линиям и почему перегрев снижает частоту процессора.</t>
+          <t xml:space="preserve">Проследите, как гипервизор делит процессор, память и диски между виртуальными машинами и где теряется производительность.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">линия 12 В, КПД, троттлинг, радиатор, термопаста, тепловой пакет</t>
+          <t xml:space="preserve">гипервизор, виртуальный диск, оверкоммит, снапшот, аппаратное ускорение</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Мобильные и встраиваемые платформы</t>
+          <t xml:space="preserve">Лекция 20. Выбор конфигурации под задачу</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,19 +915,19 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните ноутбук, планшет и встраиваемую плату по энергопотреблению, компоновке и возможностям модернизации.</t>
+          <t xml:space="preserve">Научитесь переводить требования задачи в характеристики узлов и находить узкое место до покупки, а не после.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoC, энергоэффективность, пассивное охлаждение, распаянная память, микроконтроллер</t>
+          <t xml:space="preserve">профиль нагрузки, узкое место, бюджет, запас роста, требования</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Серверные платформы</t>
+          <t xml:space="preserve">Лекция 21. Диагностика и модернизация</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,42 +945,42 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, чем сервер отличается от настольного ПК: резервирование питания, память с коррекцией и горячая замена дисков.</t>
+          <t xml:space="preserve">Разберёте порядок поиска неисправности от простых причин к сложным и научитесь отличать сбой железа от сбоя системы.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECC, резервирование, стойка, горячая замена, IPMI</t>
+          <t xml:space="preserve">признак неисправности, метод замены, журнал событий, тест памяти, замена детали</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29-30</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. Виртуализация аппаратных ресурсов</t>
+          <t xml:space="preserve">Практика 6. Виртуализация в VirtualBox; Диагностика аппаратных проблем</t>
         </is>
       </c>
       <c r="D32" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проследите, как гипервизор делит процессор, память и диски между виртуальными машинами и где теряется производительность.</t>
+          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox и разбираете учебный сбой по признакам, сдавая настройки ВМ и таблицу диагностики.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">гипервизор, виртуальный диск, оверкоммит, снапшот, аппаратное ускорение</t>
+          <t xml:space="preserve">виртуальная машина, выделение памяти, признак сбоя, порядок проверки, журнал</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 20. Выбор конфигурации под задачу</t>
+          <t xml:space="preserve">Практика 7. Модернизация учебного ПК</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Научитесь переводить требования задачи в характеристики узлов и находить узкое место до покупки, а не после.</t>
+          <t xml:space="preserve">Составляете план модернизации учебного ПК под задачу и бюджет и обосновываете замену деталей, сдавая смету и порядок работ.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">профиль нагрузки, узкое место, бюджет, запас роста, требования</t>
+          <t xml:space="preserve">узкое место, совместимость, смета, блок питания, порядок работ</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 21. Диагностика и модернизация</t>
+          <t xml:space="preserve">Практика 8. Итоговая работа: конфигурация под ИС</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте порядок поиска неисправности от простых причин к сложным и научитесь отличать сбой железа от сбоя системы.</t>
+          <t xml:space="preserve">Собираете конфигурацию под учебную информационную систему и защищаете её: требования, смета, обоснование каждого узла.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">признак неисправности, метод замены, журнал событий, тест памяти, замена детали</t>
+          <t xml:space="preserve">требования, смета, профиль нагрузки, резерв, защита конфигурации</t>
         </is>
       </c>
     </row>
